--- a/database/db/prueba4_registros_yopal.xlsx
+++ b/database/db/prueba4_registros_yopal.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$873</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$J$1:$N$873</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5797,7 +5797,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5896,7 +5896,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -25904,7 +25903,7 @@
       <c r="M558" s="36">
         <v>44321</v>
       </c>
-      <c r="N558" s="38">
+      <c r="N558" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -25939,7 +25938,7 @@
       <c r="M559" s="36">
         <v>44321</v>
       </c>
-      <c r="N559" s="38">
+      <c r="N559" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -25974,7 +25973,7 @@
       <c r="M560" s="36">
         <v>44321</v>
       </c>
-      <c r="N560" s="38">
+      <c r="N560" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -26009,7 +26008,7 @@
       <c r="M561" s="36">
         <v>44321</v>
       </c>
-      <c r="N561" s="38">
+      <c r="N561" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -26044,7 +26043,7 @@
       <c r="M562" s="36">
         <v>44321</v>
       </c>
-      <c r="N562" s="38">
+      <c r="N562" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -26079,7 +26078,7 @@
       <c r="M563" s="36">
         <v>44321</v>
       </c>
-      <c r="N563" s="38">
+      <c r="N563" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -26114,7 +26113,7 @@
       <c r="M564" s="36">
         <v>44321</v>
       </c>
-      <c r="N564" s="38">
+      <c r="N564" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -26149,7 +26148,7 @@
       <c r="M565" s="36">
         <v>44321</v>
       </c>
-      <c r="N565" s="38">
+      <c r="N565" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -26184,7 +26183,7 @@
       <c r="M566" s="36">
         <v>44321</v>
       </c>
-      <c r="N566" s="38">
+      <c r="N566" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -26219,7 +26218,7 @@
       <c r="M567" s="36">
         <v>44321</v>
       </c>
-      <c r="N567" s="38">
+      <c r="N567" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -26254,7 +26253,7 @@
       <c r="M568" s="36">
         <v>44321</v>
       </c>
-      <c r="N568" s="38">
+      <c r="N568" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -26289,7 +26288,7 @@
       <c r="M569" s="36">
         <v>44321</v>
       </c>
-      <c r="N569" s="38">
+      <c r="N569" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -26324,7 +26323,7 @@
       <c r="M570" s="36">
         <v>44321</v>
       </c>
-      <c r="N570" s="38">
+      <c r="N570" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -26359,7 +26358,7 @@
       <c r="M571" s="36">
         <v>44321</v>
       </c>
-      <c r="N571" s="38">
+      <c r="N571" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -26394,7 +26393,7 @@
       <c r="M572" s="36">
         <v>44321</v>
       </c>
-      <c r="N572" s="38">
+      <c r="N572" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -26429,7 +26428,7 @@
       <c r="M573" s="36">
         <v>44321</v>
       </c>
-      <c r="N573" s="38">
+      <c r="N573" s="36">
         <v>44302</v>
       </c>
     </row>
@@ -26464,7 +26463,7 @@
       <c r="M574" s="36">
         <v>44355</v>
       </c>
-      <c r="N574" s="38">
+      <c r="N574" s="36">
         <v>44323</v>
       </c>
     </row>
@@ -26534,7 +26533,7 @@
       <c r="M576" s="36">
         <v>44455</v>
       </c>
-      <c r="N576" s="38">
+      <c r="N576" s="36">
         <v>44417</v>
       </c>
     </row>
@@ -26569,7 +26568,7 @@
       <c r="M577" s="36">
         <v>44455</v>
       </c>
-      <c r="N577" s="38">
+      <c r="N577" s="36">
         <v>44448</v>
       </c>
     </row>
@@ -26604,7 +26603,7 @@
       <c r="M578" s="36">
         <v>44455</v>
       </c>
-      <c r="N578" s="38">
+      <c r="N578" s="36">
         <v>44448</v>
       </c>
     </row>
@@ -26639,7 +26638,7 @@
       <c r="M579" s="36">
         <v>44455</v>
       </c>
-      <c r="N579" s="38">
+      <c r="N579" s="36">
         <v>44448</v>
       </c>
     </row>
@@ -26674,7 +26673,7 @@
       <c r="M580" s="36">
         <v>44490</v>
       </c>
-      <c r="N580" s="38">
+      <c r="N580" s="36">
         <v>44484</v>
       </c>
     </row>
@@ -26709,7 +26708,7 @@
       <c r="M581" s="36">
         <v>44490</v>
       </c>
-      <c r="N581" s="38">
+      <c r="N581" s="36">
         <v>44484</v>
       </c>
     </row>
@@ -26744,7 +26743,7 @@
       <c r="M582" s="36">
         <v>44490</v>
       </c>
-      <c r="N582" s="38">
+      <c r="N582" s="36">
         <v>44484</v>
       </c>
     </row>
@@ -26779,7 +26778,7 @@
       <c r="M583" s="36">
         <v>44490</v>
       </c>
-      <c r="N583" s="38">
+      <c r="N583" s="36">
         <v>44484</v>
       </c>
     </row>
@@ -26814,7 +26813,7 @@
       <c r="M584" s="36">
         <v>44490</v>
       </c>
-      <c r="N584" s="38">
+      <c r="N584" s="36">
         <v>44484</v>
       </c>
     </row>
@@ -26849,7 +26848,7 @@
       <c r="M585" s="36">
         <v>44490</v>
       </c>
-      <c r="N585" s="38">
+      <c r="N585" s="36">
         <v>44484</v>
       </c>
     </row>
@@ -26884,7 +26883,7 @@
       <c r="M586" s="36">
         <v>44490</v>
       </c>
-      <c r="N586" s="38">
+      <c r="N586" s="36">
         <v>44484</v>
       </c>
     </row>
@@ -26919,7 +26918,7 @@
       <c r="M587" s="36">
         <v>44490</v>
       </c>
-      <c r="N587" s="38">
+      <c r="N587" s="36">
         <v>44484</v>
       </c>
     </row>
@@ -27164,7 +27163,7 @@
       <c r="M594" s="36">
         <v>44656</v>
       </c>
-      <c r="N594" s="38">
+      <c r="N594" s="36">
         <v>44578</v>
       </c>
     </row>
@@ -27199,7 +27198,7 @@
       <c r="M595" s="36">
         <v>44656</v>
       </c>
-      <c r="N595" s="38">
+      <c r="N595" s="36">
         <v>44578</v>
       </c>
     </row>
@@ -27234,7 +27233,7 @@
       <c r="M596" s="36">
         <v>44656</v>
       </c>
-      <c r="N596" s="38">
+      <c r="N596" s="36">
         <v>44578</v>
       </c>
     </row>
@@ -27269,7 +27268,7 @@
       <c r="M597" s="36">
         <v>44656</v>
       </c>
-      <c r="N597" s="38">
+      <c r="N597" s="36">
         <v>44578</v>
       </c>
     </row>
@@ -27304,7 +27303,7 @@
       <c r="M598" s="36">
         <v>44656</v>
       </c>
-      <c r="N598" s="38">
+      <c r="N598" s="36">
         <v>44578</v>
       </c>
     </row>
@@ -27339,7 +27338,7 @@
       <c r="M599" s="36">
         <v>44656</v>
       </c>
-      <c r="N599" s="38">
+      <c r="N599" s="36">
         <v>44578</v>
       </c>
     </row>
@@ -27374,7 +27373,7 @@
       <c r="M600" s="36">
         <v>44656</v>
       </c>
-      <c r="N600" s="38">
+      <c r="N600" s="36">
         <v>44578</v>
       </c>
     </row>
@@ -27409,7 +27408,7 @@
       <c r="M601" s="36">
         <v>44637</v>
       </c>
-      <c r="N601" s="38">
+      <c r="N601" s="36">
         <v>44578</v>
       </c>
     </row>
@@ -27444,7 +27443,7 @@
       <c r="M602" s="36">
         <v>44656</v>
       </c>
-      <c r="N602" s="38">
+      <c r="N602" s="36">
         <v>44578</v>
       </c>
     </row>
@@ -27479,7 +27478,7 @@
       <c r="M603" s="36">
         <v>44637</v>
       </c>
-      <c r="N603" s="38">
+      <c r="N603" s="36">
         <v>44578</v>
       </c>
     </row>
@@ -27514,7 +27513,7 @@
       <c r="M604" s="36">
         <v>44629</v>
       </c>
-      <c r="N604" s="38">
+      <c r="N604" s="36">
         <v>44606</v>
       </c>
     </row>
@@ -28354,7 +28353,7 @@
       <c r="M628" s="36">
         <v>44841</v>
       </c>
-      <c r="N628" s="38">
+      <c r="N628" s="36">
         <v>44824</v>
       </c>
     </row>
@@ -28389,7 +28388,7 @@
       <c r="M629" s="36">
         <v>44841</v>
       </c>
-      <c r="N629" s="38">
+      <c r="N629" s="36">
         <v>44824</v>
       </c>
     </row>
@@ -28424,7 +28423,7 @@
       <c r="M630" s="36">
         <v>44841</v>
       </c>
-      <c r="N630" s="38">
+      <c r="N630" s="36">
         <v>44824</v>
       </c>
     </row>
@@ -28459,7 +28458,7 @@
       <c r="M631" s="36">
         <v>44841</v>
       </c>
-      <c r="N631" s="38">
+      <c r="N631" s="36">
         <v>44824</v>
       </c>
     </row>
@@ -28494,7 +28493,7 @@
       <c r="M632" s="36">
         <v>44841</v>
       </c>
-      <c r="N632" s="38">
+      <c r="N632" s="36">
         <v>44824</v>
       </c>
     </row>
@@ -28529,7 +28528,7 @@
       <c r="M633" s="36">
         <v>44841</v>
       </c>
-      <c r="N633" s="38">
+      <c r="N633" s="36">
         <v>44824</v>
       </c>
     </row>
@@ -28564,7 +28563,7 @@
       <c r="M634" s="36">
         <v>44841</v>
       </c>
-      <c r="N634" s="38">
+      <c r="N634" s="36">
         <v>44824</v>
       </c>
     </row>
@@ -28599,7 +28598,7 @@
       <c r="M635" s="36">
         <v>44841</v>
       </c>
-      <c r="N635" s="38">
+      <c r="N635" s="36">
         <v>44824</v>
       </c>
     </row>
@@ -28622,7 +28621,7 @@
       <c r="G636" s="9"/>
       <c r="H636" s="9"/>
       <c r="I636" s="9"/>
-      <c r="J636" s="39" t="s">
+      <c r="J636" s="38" t="s">
         <v>1195</v>
       </c>
       <c r="K636" s="8" t="s">
@@ -28657,7 +28656,7 @@
       <c r="G637" s="9"/>
       <c r="H637" s="9"/>
       <c r="I637" s="9"/>
-      <c r="J637" s="39" t="s">
+      <c r="J637" s="38" t="s">
         <v>1197</v>
       </c>
       <c r="K637" s="8" t="s">
@@ -28692,7 +28691,7 @@
       <c r="G638" s="9"/>
       <c r="H638" s="9"/>
       <c r="I638" s="9"/>
-      <c r="J638" s="39" t="s">
+      <c r="J638" s="38" t="s">
         <v>1199</v>
       </c>
       <c r="K638" s="8" t="s">
@@ -28727,7 +28726,7 @@
       <c r="G639" s="9"/>
       <c r="H639" s="9"/>
       <c r="I639" s="9"/>
-      <c r="J639" s="39" t="s">
+      <c r="J639" s="38" t="s">
         <v>1201</v>
       </c>
       <c r="K639" s="8" t="s">
@@ -28762,7 +28761,7 @@
       <c r="G640" s="9"/>
       <c r="H640" s="9"/>
       <c r="I640" s="9"/>
-      <c r="J640" s="39" t="s">
+      <c r="J640" s="38" t="s">
         <v>1203</v>
       </c>
       <c r="K640" s="8" t="s">
@@ -28797,7 +28796,7 @@
       <c r="G641" s="9"/>
       <c r="H641" s="9"/>
       <c r="I641" s="9"/>
-      <c r="J641" s="39" t="s">
+      <c r="J641" s="38" t="s">
         <v>1205</v>
       </c>
       <c r="K641" s="8" t="s">
@@ -28832,7 +28831,7 @@
       <c r="G642" s="9"/>
       <c r="H642" s="9"/>
       <c r="I642" s="9"/>
-      <c r="J642" s="39" t="s">
+      <c r="J642" s="38" t="s">
         <v>1207</v>
       </c>
       <c r="K642" s="8" t="s">
@@ -28867,7 +28866,7 @@
       <c r="G643" s="9"/>
       <c r="H643" s="9"/>
       <c r="I643" s="9"/>
-      <c r="J643" s="39" t="s">
+      <c r="J643" s="38" t="s">
         <v>1209</v>
       </c>
       <c r="K643" s="8" t="s">
@@ -28902,7 +28901,7 @@
       <c r="G644" s="9"/>
       <c r="H644" s="9"/>
       <c r="I644" s="9"/>
-      <c r="J644" s="39" t="s">
+      <c r="J644" s="38" t="s">
         <v>1211</v>
       </c>
       <c r="K644" s="8" t="s">
@@ -28911,7 +28910,7 @@
       <c r="L644" s="8">
         <v>214000</v>
       </c>
-      <c r="M644" s="40">
+      <c r="M644" s="39">
         <v>44868</v>
       </c>
       <c r="N644" s="24">
@@ -28937,7 +28936,7 @@
       <c r="G645" s="9"/>
       <c r="H645" s="9"/>
       <c r="I645" s="9"/>
-      <c r="J645" s="39" t="s">
+      <c r="J645" s="38" t="s">
         <v>1213</v>
       </c>
       <c r="K645" s="8" t="s">
@@ -28972,7 +28971,7 @@
       <c r="G646" s="9"/>
       <c r="H646" s="9"/>
       <c r="I646" s="9"/>
-      <c r="J646" s="39" t="s">
+      <c r="J646" s="38" t="s">
         <v>1215</v>
       </c>
       <c r="K646" s="8" t="s">
@@ -29007,7 +29006,7 @@
       <c r="G647" s="9"/>
       <c r="H647" s="9"/>
       <c r="I647" s="9"/>
-      <c r="J647" s="39" t="s">
+      <c r="J647" s="38" t="s">
         <v>1217</v>
       </c>
       <c r="K647" s="8" t="s">
@@ -29042,7 +29041,7 @@
       <c r="G648" s="9"/>
       <c r="H648" s="9"/>
       <c r="I648" s="9"/>
-      <c r="J648" s="39" t="s">
+      <c r="J648" s="38" t="s">
         <v>1219</v>
       </c>
       <c r="K648" s="8" t="s">
@@ -29077,7 +29076,7 @@
       <c r="G649" s="9"/>
       <c r="H649" s="9"/>
       <c r="I649" s="9"/>
-      <c r="J649" s="39" t="s">
+      <c r="J649" s="38" t="s">
         <v>1221</v>
       </c>
       <c r="K649" s="8" t="s">
@@ -29112,7 +29111,7 @@
       <c r="G650" s="9"/>
       <c r="H650" s="9"/>
       <c r="I650" s="9"/>
-      <c r="J650" s="39" t="s">
+      <c r="J650" s="38" t="s">
         <v>1223</v>
       </c>
       <c r="K650" s="8" t="s">
@@ -29147,7 +29146,7 @@
       <c r="G651" s="9"/>
       <c r="H651" s="9"/>
       <c r="I651" s="9"/>
-      <c r="J651" s="39" t="s">
+      <c r="J651" s="38" t="s">
         <v>1225</v>
       </c>
       <c r="K651" s="8" t="s">
@@ -29182,7 +29181,7 @@
       <c r="G652" s="9"/>
       <c r="H652" s="9"/>
       <c r="I652" s="9"/>
-      <c r="J652" s="39" t="s">
+      <c r="J652" s="38" t="s">
         <v>1227</v>
       </c>
       <c r="K652" s="8" t="s">
@@ -29217,7 +29216,7 @@
       <c r="G653" s="9"/>
       <c r="H653" s="9"/>
       <c r="I653" s="9"/>
-      <c r="J653" s="39" t="s">
+      <c r="J653" s="38" t="s">
         <v>1229</v>
       </c>
       <c r="K653" s="8" t="s">
@@ -29252,7 +29251,7 @@
       <c r="G654" s="9"/>
       <c r="H654" s="9"/>
       <c r="I654" s="9"/>
-      <c r="J654" s="39" t="s">
+      <c r="J654" s="38" t="s">
         <v>1231</v>
       </c>
       <c r="K654" s="8" t="s">
@@ -29287,7 +29286,7 @@
       <c r="G655" s="9"/>
       <c r="H655" s="9"/>
       <c r="I655" s="9"/>
-      <c r="J655" s="39" t="s">
+      <c r="J655" s="38" t="s">
         <v>1233</v>
       </c>
       <c r="K655" s="8" t="s">
@@ -29322,7 +29321,7 @@
       <c r="G656" s="9"/>
       <c r="H656" s="9"/>
       <c r="I656" s="9"/>
-      <c r="J656" s="39" t="s">
+      <c r="J656" s="38" t="s">
         <v>1235</v>
       </c>
       <c r="K656" s="8" t="s">
@@ -29357,7 +29356,7 @@
       <c r="G657" s="9"/>
       <c r="H657" s="9"/>
       <c r="I657" s="9"/>
-      <c r="J657" s="39" t="s">
+      <c r="J657" s="38" t="s">
         <v>1237</v>
       </c>
       <c r="K657" s="8" t="s">
@@ -29392,7 +29391,7 @@
       <c r="G658" s="9"/>
       <c r="H658" s="9"/>
       <c r="I658" s="9"/>
-      <c r="J658" s="39" t="s">
+      <c r="J658" s="38" t="s">
         <v>1239</v>
       </c>
       <c r="K658" s="8" t="s">
@@ -29427,7 +29426,7 @@
       <c r="G659" s="9"/>
       <c r="H659" s="9"/>
       <c r="I659" s="9"/>
-      <c r="J659" s="39" t="s">
+      <c r="J659" s="38" t="s">
         <v>1241</v>
       </c>
       <c r="K659" s="8" t="s">
@@ -29462,7 +29461,7 @@
       <c r="G660" s="9"/>
       <c r="H660" s="9"/>
       <c r="I660" s="9"/>
-      <c r="J660" s="39" t="s">
+      <c r="J660" s="38" t="s">
         <v>1243</v>
       </c>
       <c r="K660" s="8" t="s">
@@ -29497,7 +29496,7 @@
       <c r="G661" s="9"/>
       <c r="H661" s="9"/>
       <c r="I661" s="9"/>
-      <c r="J661" s="39" t="s">
+      <c r="J661" s="38" t="s">
         <v>1245</v>
       </c>
       <c r="K661" s="8" t="s">
@@ -29532,7 +29531,7 @@
       <c r="G662" s="9"/>
       <c r="H662" s="9"/>
       <c r="I662" s="9"/>
-      <c r="J662" s="39" t="s">
+      <c r="J662" s="38" t="s">
         <v>1247</v>
       </c>
       <c r="K662" s="8" t="s">
@@ -29567,7 +29566,7 @@
       <c r="G663" s="9"/>
       <c r="H663" s="9"/>
       <c r="I663" s="9"/>
-      <c r="J663" s="39" t="s">
+      <c r="J663" s="38" t="s">
         <v>1249</v>
       </c>
       <c r="K663" s="8" t="s">
@@ -29602,7 +29601,7 @@
       <c r="G664" s="9"/>
       <c r="H664" s="9"/>
       <c r="I664" s="9"/>
-      <c r="J664" s="39" t="s">
+      <c r="J664" s="38" t="s">
         <v>1251</v>
       </c>
       <c r="K664" s="8" t="s">
@@ -29637,7 +29636,7 @@
       <c r="G665" s="9"/>
       <c r="H665" s="9"/>
       <c r="I665" s="9"/>
-      <c r="J665" s="39" t="s">
+      <c r="J665" s="38" t="s">
         <v>1253</v>
       </c>
       <c r="K665" s="8" t="s">
@@ -29672,7 +29671,7 @@
       <c r="G666" s="9"/>
       <c r="H666" s="9"/>
       <c r="I666" s="9"/>
-      <c r="J666" s="39" t="s">
+      <c r="J666" s="38" t="s">
         <v>1255</v>
       </c>
       <c r="K666" s="8" t="s">
@@ -29707,7 +29706,7 @@
       <c r="G667" s="9"/>
       <c r="H667" s="9"/>
       <c r="I667" s="9"/>
-      <c r="J667" s="39" t="s">
+      <c r="J667" s="38" t="s">
         <v>1257</v>
       </c>
       <c r="K667" s="8" t="s">
@@ -29742,7 +29741,7 @@
       <c r="G668" s="9"/>
       <c r="H668" s="9"/>
       <c r="I668" s="9"/>
-      <c r="J668" s="39" t="s">
+      <c r="J668" s="38" t="s">
         <v>1259</v>
       </c>
       <c r="K668" s="8" t="s">
@@ -29821,7 +29820,7 @@
       <c r="L670" s="8">
         <v>155000</v>
       </c>
-      <c r="M670" s="40">
+      <c r="M670" s="39">
         <v>44986</v>
       </c>
       <c r="N670" s="24">
@@ -29847,7 +29846,7 @@
       <c r="G671" s="9"/>
       <c r="H671" s="9"/>
       <c r="I671" s="9"/>
-      <c r="J671" s="39" t="s">
+      <c r="J671" s="38" t="s">
         <v>1265</v>
       </c>
       <c r="K671" s="8" t="s">
@@ -29856,7 +29855,7 @@
       <c r="L671" s="8">
         <v>155000</v>
       </c>
-      <c r="M671" s="40">
+      <c r="M671" s="39">
         <v>44986</v>
       </c>
       <c r="N671" s="24">
@@ -29882,7 +29881,7 @@
       <c r="G672" s="9"/>
       <c r="H672" s="9"/>
       <c r="I672" s="9"/>
-      <c r="J672" s="39" t="s">
+      <c r="J672" s="38" t="s">
         <v>1267</v>
       </c>
       <c r="K672" s="8" t="s">
@@ -29891,7 +29890,7 @@
       <c r="L672" s="8">
         <v>155000</v>
       </c>
-      <c r="M672" s="40">
+      <c r="M672" s="39">
         <v>44986</v>
       </c>
       <c r="N672" s="24">
@@ -29926,7 +29925,7 @@
       <c r="L673" s="8">
         <v>105000</v>
       </c>
-      <c r="M673" s="40">
+      <c r="M673" s="39">
         <v>44986</v>
       </c>
       <c r="N673" s="24">
@@ -29961,7 +29960,7 @@
       <c r="L674" s="8">
         <v>105000</v>
       </c>
-      <c r="M674" s="40">
+      <c r="M674" s="39">
         <v>44986</v>
       </c>
       <c r="N674" s="24">
@@ -29996,7 +29995,7 @@
       <c r="L675" s="8">
         <v>105000</v>
       </c>
-      <c r="M675" s="40">
+      <c r="M675" s="39">
         <v>44986</v>
       </c>
       <c r="N675" s="24">
@@ -30031,7 +30030,7 @@
       <c r="L676" s="8">
         <v>155000</v>
       </c>
-      <c r="M676" s="40">
+      <c r="M676" s="39">
         <v>44986</v>
       </c>
       <c r="N676" s="24">
@@ -30066,7 +30065,7 @@
       <c r="L677" s="8">
         <v>105000</v>
       </c>
-      <c r="M677" s="40">
+      <c r="M677" s="39">
         <v>44986</v>
       </c>
       <c r="N677" s="24">
@@ -30101,7 +30100,7 @@
       <c r="L678" s="8">
         <v>155000</v>
       </c>
-      <c r="M678" s="40">
+      <c r="M678" s="39">
         <v>44986</v>
       </c>
       <c r="N678" s="24">
@@ -30136,10 +30135,10 @@
       <c r="L679" s="8">
         <v>155000</v>
       </c>
-      <c r="M679" s="40">
+      <c r="M679" s="39">
         <v>44986</v>
       </c>
-      <c r="N679" s="40">
+      <c r="N679" s="39">
         <v>44964</v>
       </c>
     </row>
@@ -30171,10 +30170,10 @@
       <c r="L680" s="8">
         <v>155000</v>
       </c>
-      <c r="M680" s="40">
+      <c r="M680" s="39">
         <v>44986</v>
       </c>
-      <c r="N680" s="40">
+      <c r="N680" s="39">
         <v>44964</v>
       </c>
     </row>
@@ -30206,10 +30205,10 @@
       <c r="L681" s="8">
         <v>155000</v>
       </c>
-      <c r="M681" s="40">
+      <c r="M681" s="39">
         <v>44986</v>
       </c>
-      <c r="N681" s="40">
+      <c r="N681" s="39">
         <v>44964</v>
       </c>
     </row>
@@ -30244,7 +30243,7 @@
       <c r="M682" s="36">
         <v>45700</v>
       </c>
-      <c r="N682" s="38">
+      <c r="N682" s="36">
         <v>45687</v>
       </c>
     </row>
@@ -30267,7 +30266,7 @@
       <c r="G683" s="9"/>
       <c r="H683" s="9"/>
       <c r="I683" s="9"/>
-      <c r="J683" s="39" t="s">
+      <c r="J683" s="38" t="s">
         <v>1289</v>
       </c>
       <c r="K683" s="8" t="s">
@@ -30276,7 +30275,7 @@
       <c r="L683" s="8">
         <v>277986</v>
       </c>
-      <c r="M683" s="40">
+      <c r="M683" s="39">
         <v>45700</v>
       </c>
       <c r="N683" s="24">
@@ -30302,7 +30301,7 @@
       <c r="G684" s="9"/>
       <c r="H684" s="9"/>
       <c r="I684" s="9"/>
-      <c r="J684" s="39" t="s">
+      <c r="J684" s="38" t="s">
         <v>1291</v>
       </c>
       <c r="K684" s="8" t="s">
@@ -30311,7 +30310,7 @@
       <c r="L684" s="8">
         <v>138993</v>
       </c>
-      <c r="M684" s="40">
+      <c r="M684" s="39">
         <v>45700</v>
       </c>
       <c r="N684" s="24">
@@ -30337,7 +30336,7 @@
       <c r="G685" s="9"/>
       <c r="H685" s="9"/>
       <c r="I685" s="9"/>
-      <c r="J685" s="39" t="s">
+      <c r="J685" s="38" t="s">
         <v>1293</v>
       </c>
       <c r="K685" s="8" t="s">
@@ -30346,7 +30345,7 @@
       <c r="L685" s="8">
         <v>277986</v>
       </c>
-      <c r="M685" s="40">
+      <c r="M685" s="39">
         <v>45700</v>
       </c>
       <c r="N685" s="24">
@@ -30372,7 +30371,7 @@
       <c r="G686" s="9"/>
       <c r="H686" s="9"/>
       <c r="I686" s="9"/>
-      <c r="J686" s="39" t="s">
+      <c r="J686" s="38" t="s">
         <v>1295</v>
       </c>
       <c r="K686" s="8" t="s">
@@ -30381,7 +30380,7 @@
       <c r="L686" s="8">
         <v>277986</v>
       </c>
-      <c r="M686" s="40">
+      <c r="M686" s="39">
         <v>45700</v>
       </c>
       <c r="N686" s="24">
@@ -30407,7 +30406,7 @@
       <c r="G687" s="9"/>
       <c r="H687" s="9"/>
       <c r="I687" s="9"/>
-      <c r="J687" s="39" t="s">
+      <c r="J687" s="38" t="s">
         <v>1297</v>
       </c>
       <c r="K687" s="8" t="s">
@@ -30416,7 +30415,7 @@
       <c r="L687" s="8">
         <v>277986</v>
       </c>
-      <c r="M687" s="40">
+      <c r="M687" s="39">
         <v>45700</v>
       </c>
       <c r="N687" s="24">
@@ -30442,7 +30441,7 @@
       <c r="G688" s="9"/>
       <c r="H688" s="9"/>
       <c r="I688" s="9"/>
-      <c r="J688" s="39" t="s">
+      <c r="J688" s="38" t="s">
         <v>1299</v>
       </c>
       <c r="K688" s="8" t="s">
@@ -30451,7 +30450,7 @@
       <c r="L688" s="8">
         <v>277986</v>
       </c>
-      <c r="M688" s="40">
+      <c r="M688" s="39">
         <v>45700</v>
       </c>
       <c r="N688" s="24">
@@ -30477,7 +30476,7 @@
       <c r="G689" s="9"/>
       <c r="H689" s="9"/>
       <c r="I689" s="9"/>
-      <c r="J689" s="39" t="s">
+      <c r="J689" s="38" t="s">
         <v>1301</v>
       </c>
       <c r="K689" s="8" t="s">
@@ -30486,7 +30485,7 @@
       <c r="L689" s="8">
         <v>277986</v>
       </c>
-      <c r="M689" s="40">
+      <c r="M689" s="39">
         <v>45700</v>
       </c>
       <c r="N689" s="24">
@@ -30512,7 +30511,7 @@
       <c r="G690" s="9"/>
       <c r="H690" s="9"/>
       <c r="I690" s="9"/>
-      <c r="J690" s="39" t="s">
+      <c r="J690" s="38" t="s">
         <v>1303</v>
       </c>
       <c r="K690" s="8" t="s">
@@ -30521,7 +30520,7 @@
       <c r="L690" s="8">
         <v>277986</v>
       </c>
-      <c r="M690" s="40">
+      <c r="M690" s="39">
         <v>45700</v>
       </c>
       <c r="N690" s="24">
@@ -30547,7 +30546,7 @@
       <c r="G691" s="9"/>
       <c r="H691" s="9"/>
       <c r="I691" s="9"/>
-      <c r="J691" s="39" t="s">
+      <c r="J691" s="38" t="s">
         <v>1305</v>
       </c>
       <c r="K691" s="8" t="s">
@@ -30556,7 +30555,7 @@
       <c r="L691" s="8">
         <v>277986</v>
       </c>
-      <c r="M691" s="40">
+      <c r="M691" s="39">
         <v>45700</v>
       </c>
       <c r="N691" s="24">
@@ -30582,7 +30581,7 @@
       <c r="G692" s="9"/>
       <c r="H692" s="9"/>
       <c r="I692" s="9"/>
-      <c r="J692" s="39" t="s">
+      <c r="J692" s="38" t="s">
         <v>1307</v>
       </c>
       <c r="K692" s="8" t="s">
@@ -30617,7 +30616,7 @@
       <c r="G693" s="9"/>
       <c r="H693" s="9"/>
       <c r="I693" s="9"/>
-      <c r="J693" s="39" t="s">
+      <c r="J693" s="38" t="s">
         <v>1309</v>
       </c>
       <c r="K693" s="8" t="s">
@@ -30652,7 +30651,7 @@
       <c r="G694" s="9"/>
       <c r="H694" s="9"/>
       <c r="I694" s="9"/>
-      <c r="J694" s="39" t="s">
+      <c r="J694" s="38" t="s">
         <v>1311</v>
       </c>
       <c r="K694" s="8" t="s">
@@ -30687,7 +30686,7 @@
       <c r="G695" s="9"/>
       <c r="H695" s="9"/>
       <c r="I695" s="9"/>
-      <c r="J695" s="39" t="s">
+      <c r="J695" s="38" t="s">
         <v>1313</v>
       </c>
       <c r="K695" s="8" t="s">
@@ -30699,7 +30698,7 @@
       <c r="M695" s="36">
         <v>45783</v>
       </c>
-      <c r="N695" s="41">
+      <c r="N695" s="40">
         <v>45736</v>
       </c>
     </row>
@@ -30722,7 +30721,7 @@
       <c r="G696" s="9"/>
       <c r="H696" s="9"/>
       <c r="I696" s="9"/>
-      <c r="J696" s="39" t="s">
+      <c r="J696" s="38" t="s">
         <v>1315</v>
       </c>
       <c r="K696" s="8" t="s">
@@ -30734,7 +30733,7 @@
       <c r="M696" s="36">
         <v>45783</v>
       </c>
-      <c r="N696" s="41">
+      <c r="N696" s="40">
         <v>45736</v>
       </c>
     </row>
@@ -30757,7 +30756,7 @@
       <c r="G697" s="9"/>
       <c r="H697" s="9"/>
       <c r="I697" s="9"/>
-      <c r="J697" s="39" t="s">
+      <c r="J697" s="38" t="s">
         <v>1317</v>
       </c>
       <c r="K697" s="8" t="s">
@@ -30769,7 +30768,7 @@
       <c r="M697" s="36">
         <v>45783</v>
       </c>
-      <c r="N697" s="41">
+      <c r="N697" s="40">
         <v>45736</v>
       </c>
     </row>
@@ -30792,7 +30791,7 @@
       <c r="G698" s="9"/>
       <c r="H698" s="9"/>
       <c r="I698" s="9"/>
-      <c r="J698" s="39" t="s">
+      <c r="J698" s="38" t="s">
         <v>1319</v>
       </c>
       <c r="K698" s="8" t="s">
@@ -30804,7 +30803,7 @@
       <c r="M698" s="36">
         <v>45783</v>
       </c>
-      <c r="N698" s="41">
+      <c r="N698" s="40">
         <v>45736</v>
       </c>
     </row>
@@ -30827,7 +30826,7 @@
       <c r="G699" s="9"/>
       <c r="H699" s="9"/>
       <c r="I699" s="9"/>
-      <c r="J699" s="39" t="s">
+      <c r="J699" s="38" t="s">
         <v>1321</v>
       </c>
       <c r="K699" s="8" t="s">
@@ -30839,7 +30838,7 @@
       <c r="M699" s="36">
         <v>45783</v>
       </c>
-      <c r="N699" s="41">
+      <c r="N699" s="40">
         <v>45736</v>
       </c>
     </row>
@@ -30862,7 +30861,7 @@
       <c r="G700" s="9"/>
       <c r="H700" s="9"/>
       <c r="I700" s="9"/>
-      <c r="J700" s="39" t="s">
+      <c r="J700" s="38" t="s">
         <v>1323</v>
       </c>
       <c r="K700" s="8" t="s">
@@ -30874,7 +30873,7 @@
       <c r="M700" s="36">
         <v>45783</v>
       </c>
-      <c r="N700" s="41">
+      <c r="N700" s="40">
         <v>45736</v>
       </c>
     </row>
@@ -30897,7 +30896,7 @@
       <c r="G701" s="9"/>
       <c r="H701" s="9"/>
       <c r="I701" s="9"/>
-      <c r="J701" s="39" t="s">
+      <c r="J701" s="38" t="s">
         <v>1325</v>
       </c>
       <c r="K701" s="8" t="s">
@@ -30909,7 +30908,7 @@
       <c r="M701" s="36">
         <v>45783</v>
       </c>
-      <c r="N701" s="41">
+      <c r="N701" s="40">
         <v>45736</v>
       </c>
     </row>
@@ -30932,7 +30931,7 @@
       <c r="G702" s="9"/>
       <c r="H702" s="9"/>
       <c r="I702" s="9"/>
-      <c r="J702" s="39" t="s">
+      <c r="J702" s="38" t="s">
         <v>1327</v>
       </c>
       <c r="K702" s="8" t="s">
@@ -30944,7 +30943,7 @@
       <c r="M702" s="36">
         <v>45783</v>
       </c>
-      <c r="N702" s="41">
+      <c r="N702" s="40">
         <v>45736</v>
       </c>
     </row>
@@ -30967,7 +30966,7 @@
       <c r="G703" s="9"/>
       <c r="H703" s="9"/>
       <c r="I703" s="9"/>
-      <c r="J703" s="39" t="s">
+      <c r="J703" s="38" t="s">
         <v>1329</v>
       </c>
       <c r="K703" s="8" t="s">
@@ -30979,7 +30978,7 @@
       <c r="M703" s="36">
         <v>45783</v>
       </c>
-      <c r="N703" s="41">
+      <c r="N703" s="40">
         <v>45736</v>
       </c>
     </row>
@@ -31002,7 +31001,7 @@
       <c r="G704" s="9"/>
       <c r="H704" s="9"/>
       <c r="I704" s="9"/>
-      <c r="J704" s="39" t="s">
+      <c r="J704" s="38" t="s">
         <v>1331</v>
       </c>
       <c r="K704" s="8" t="s">
@@ -31014,7 +31013,7 @@
       <c r="M704" s="36">
         <v>45783</v>
       </c>
-      <c r="N704" s="41">
+      <c r="N704" s="40">
         <v>45736</v>
       </c>
     </row>
@@ -31037,7 +31036,7 @@
       <c r="G705" s="9"/>
       <c r="H705" s="9"/>
       <c r="I705" s="9"/>
-      <c r="J705" s="39" t="s">
+      <c r="J705" s="38" t="s">
         <v>1333</v>
       </c>
       <c r="K705" s="8" t="s">
@@ -31049,7 +31048,7 @@
       <c r="M705" s="36">
         <v>45783</v>
       </c>
-      <c r="N705" s="41">
+      <c r="N705" s="40">
         <v>45736</v>
       </c>
     </row>
@@ -31072,7 +31071,7 @@
       <c r="G706" s="9"/>
       <c r="H706" s="9"/>
       <c r="I706" s="9"/>
-      <c r="J706" s="39" t="s">
+      <c r="J706" s="38" t="s">
         <v>1335</v>
       </c>
       <c r="K706" s="8" t="s">
@@ -31084,7 +31083,7 @@
       <c r="M706" s="36">
         <v>45783</v>
       </c>
-      <c r="N706" s="41">
+      <c r="N706" s="40">
         <v>45736</v>
       </c>
     </row>
@@ -31119,7 +31118,7 @@
       <c r="M707" s="36">
         <v>45783</v>
       </c>
-      <c r="N707" s="41">
+      <c r="N707" s="40">
         <v>45736</v>
       </c>
     </row>
@@ -31142,7 +31141,7 @@
       <c r="G708" s="9"/>
       <c r="H708" s="9"/>
       <c r="I708" s="9"/>
-      <c r="J708" s="39" t="s">
+      <c r="J708" s="38" t="s">
         <v>1339</v>
       </c>
       <c r="K708" s="8" t="s">
@@ -31177,7 +31176,7 @@
       <c r="G709" s="9"/>
       <c r="H709" s="9"/>
       <c r="I709" s="9"/>
-      <c r="J709" s="39" t="s">
+      <c r="J709" s="38" t="s">
         <v>1341</v>
       </c>
       <c r="K709" s="8" t="s">
@@ -31212,7 +31211,7 @@
       <c r="G710" s="9"/>
       <c r="H710" s="9"/>
       <c r="I710" s="9"/>
-      <c r="J710" s="39" t="s">
+      <c r="J710" s="38" t="s">
         <v>1343</v>
       </c>
       <c r="K710" s="8" t="s">
@@ -31247,7 +31246,7 @@
       <c r="G711" s="9"/>
       <c r="H711" s="9"/>
       <c r="I711" s="9"/>
-      <c r="J711" s="39" t="s">
+      <c r="J711" s="38" t="s">
         <v>1345</v>
       </c>
       <c r="K711" s="8" t="s">
@@ -31282,7 +31281,7 @@
       <c r="G712" s="9"/>
       <c r="H712" s="9"/>
       <c r="I712" s="9"/>
-      <c r="J712" s="39" t="s">
+      <c r="J712" s="38" t="s">
         <v>1347</v>
       </c>
       <c r="K712" s="8" t="s">
@@ -31317,7 +31316,7 @@
       <c r="G713" s="9"/>
       <c r="H713" s="9"/>
       <c r="I713" s="9"/>
-      <c r="J713" s="39" t="s">
+      <c r="J713" s="38" t="s">
         <v>1349</v>
       </c>
       <c r="K713" s="8" t="s">
@@ -31352,7 +31351,7 @@
       <c r="G714" s="9"/>
       <c r="H714" s="9"/>
       <c r="I714" s="9"/>
-      <c r="J714" s="39" t="s">
+      <c r="J714" s="38" t="s">
         <v>1351</v>
       </c>
       <c r="K714" s="8" t="s">
@@ -31387,7 +31386,7 @@
       <c r="G715" s="9"/>
       <c r="H715" s="9"/>
       <c r="I715" s="9"/>
-      <c r="J715" s="39" t="s">
+      <c r="J715" s="38" t="s">
         <v>1353</v>
       </c>
       <c r="K715" s="8" t="s">
@@ -31422,7 +31421,7 @@
       <c r="G716" s="9"/>
       <c r="H716" s="9"/>
       <c r="I716" s="9"/>
-      <c r="J716" s="39" t="s">
+      <c r="J716" s="38" t="s">
         <v>1355</v>
       </c>
       <c r="K716" s="8" t="s">
@@ -31457,7 +31456,7 @@
       <c r="G717" s="9"/>
       <c r="H717" s="9"/>
       <c r="I717" s="9"/>
-      <c r="J717" s="39" t="s">
+      <c r="J717" s="38" t="s">
         <v>1357</v>
       </c>
       <c r="K717" s="8" t="s">
@@ -31492,7 +31491,7 @@
       <c r="G718" s="9"/>
       <c r="H718" s="9"/>
       <c r="I718" s="9"/>
-      <c r="J718" s="39" t="s">
+      <c r="J718" s="38" t="s">
         <v>1359</v>
       </c>
       <c r="K718" s="8" t="s">
@@ -31527,7 +31526,7 @@
       <c r="G719" s="9"/>
       <c r="H719" s="9"/>
       <c r="I719" s="9"/>
-      <c r="J719" s="39" t="s">
+      <c r="J719" s="38" t="s">
         <v>1361</v>
       </c>
       <c r="K719" s="8" t="s">
@@ -31562,7 +31561,7 @@
       <c r="G720" s="9"/>
       <c r="H720" s="9"/>
       <c r="I720" s="9"/>
-      <c r="J720" s="39" t="s">
+      <c r="J720" s="38" t="s">
         <v>1363</v>
       </c>
       <c r="K720" s="8" t="s">
@@ -31632,7 +31631,7 @@
       <c r="G722" s="9"/>
       <c r="H722" s="9"/>
       <c r="I722" s="9"/>
-      <c r="J722" s="39" t="s">
+      <c r="J722" s="38" t="s">
         <v>1367</v>
       </c>
       <c r="K722" s="8" t="s">
@@ -31641,7 +31640,7 @@
       <c r="L722" s="8">
         <v>308754</v>
       </c>
-      <c r="M722" s="40">
+      <c r="M722" s="39">
         <v>45784</v>
       </c>
       <c r="N722" s="24">
@@ -31667,7 +31666,7 @@
       <c r="G723" s="9"/>
       <c r="H723" s="9"/>
       <c r="I723" s="9"/>
-      <c r="J723" s="39" t="s">
+      <c r="J723" s="38" t="s">
         <v>1369</v>
       </c>
       <c r="K723" s="8" t="s">
@@ -31676,7 +31675,7 @@
       <c r="L723" s="8">
         <v>308754</v>
       </c>
-      <c r="M723" s="40">
+      <c r="M723" s="39">
         <v>45784</v>
       </c>
       <c r="N723" s="24">
@@ -31702,7 +31701,7 @@
       <c r="G724" s="9"/>
       <c r="H724" s="9"/>
       <c r="I724" s="9"/>
-      <c r="J724" s="39" t="s">
+      <c r="J724" s="38" t="s">
         <v>1371</v>
       </c>
       <c r="K724" s="8" t="s">
@@ -31737,7 +31736,7 @@
       <c r="G725" s="9"/>
       <c r="H725" s="9"/>
       <c r="I725" s="9"/>
-      <c r="J725" s="39" t="s">
+      <c r="J725" s="38" t="s">
         <v>1373</v>
       </c>
       <c r="K725" s="8" t="s">
@@ -31772,7 +31771,7 @@
       <c r="G726" s="9"/>
       <c r="H726" s="9"/>
       <c r="I726" s="9"/>
-      <c r="J726" s="39" t="s">
+      <c r="J726" s="38" t="s">
         <v>1375</v>
       </c>
       <c r="K726" s="8" t="s">
@@ -31807,7 +31806,7 @@
       <c r="G727" s="9"/>
       <c r="H727" s="9"/>
       <c r="I727" s="9"/>
-      <c r="J727" s="39" t="s">
+      <c r="J727" s="38" t="s">
         <v>1377</v>
       </c>
       <c r="K727" s="8" t="s">
@@ -31842,7 +31841,7 @@
       <c r="G728" s="9"/>
       <c r="H728" s="9"/>
       <c r="I728" s="9"/>
-      <c r="J728" s="39" t="s">
+      <c r="J728" s="38" t="s">
         <v>1379</v>
       </c>
       <c r="K728" s="8" t="s">
@@ -31877,7 +31876,7 @@
       <c r="G729" s="9"/>
       <c r="H729" s="9"/>
       <c r="I729" s="9"/>
-      <c r="J729" s="39" t="s">
+      <c r="J729" s="38" t="s">
         <v>1381</v>
       </c>
       <c r="K729" s="8" t="s">
@@ -31912,7 +31911,7 @@
       <c r="G730" s="9"/>
       <c r="H730" s="9"/>
       <c r="I730" s="9"/>
-      <c r="J730" s="39" t="s">
+      <c r="J730" s="38" t="s">
         <v>1383</v>
       </c>
       <c r="K730" s="8" t="s">
@@ -31947,7 +31946,7 @@
       <c r="G731" s="9"/>
       <c r="H731" s="9"/>
       <c r="I731" s="9"/>
-      <c r="J731" s="39" t="s">
+      <c r="J731" s="38" t="s">
         <v>1385</v>
       </c>
       <c r="K731" s="8" t="s">
@@ -31982,7 +31981,7 @@
       <c r="G732" s="9"/>
       <c r="H732" s="9"/>
       <c r="I732" s="9"/>
-      <c r="J732" s="39" t="s">
+      <c r="J732" s="38" t="s">
         <v>1387</v>
       </c>
       <c r="K732" s="8" t="s">
@@ -32017,7 +32016,7 @@
       <c r="G733" s="9"/>
       <c r="H733" s="9"/>
       <c r="I733" s="9"/>
-      <c r="J733" s="39" t="s">
+      <c r="J733" s="38" t="s">
         <v>1389</v>
       </c>
       <c r="K733" s="8" t="s">
@@ -32052,7 +32051,7 @@
       <c r="G734" s="9"/>
       <c r="H734" s="9"/>
       <c r="I734" s="9"/>
-      <c r="J734" s="39" t="s">
+      <c r="J734" s="38" t="s">
         <v>1391</v>
       </c>
       <c r="K734" s="8" t="s">
@@ -32087,7 +32086,7 @@
       <c r="G735" s="9"/>
       <c r="H735" s="9"/>
       <c r="I735" s="9"/>
-      <c r="J735" s="39" t="s">
+      <c r="J735" s="38" t="s">
         <v>1393</v>
       </c>
       <c r="K735" s="8" t="s">
@@ -32122,7 +32121,7 @@
       <c r="G736" s="9"/>
       <c r="H736" s="9"/>
       <c r="I736" s="9"/>
-      <c r="J736" s="39" t="s">
+      <c r="J736" s="38" t="s">
         <v>1395</v>
       </c>
       <c r="K736" s="8" t="s">
@@ -32717,7 +32716,7 @@
       <c r="G753" s="9"/>
       <c r="H753" s="9"/>
       <c r="I753" s="9"/>
-      <c r="J753" s="39" t="s">
+      <c r="J753" s="38" t="s">
         <v>1429</v>
       </c>
       <c r="K753" s="8" t="s">
@@ -32752,7 +32751,7 @@
       <c r="G754" s="9"/>
       <c r="H754" s="9"/>
       <c r="I754" s="9"/>
-      <c r="J754" s="39" t="s">
+      <c r="J754" s="38" t="s">
         <v>1431</v>
       </c>
       <c r="K754" s="8" t="s">
@@ -32787,7 +32786,7 @@
       <c r="G755" s="9"/>
       <c r="H755" s="9"/>
       <c r="I755" s="9"/>
-      <c r="J755" s="39" t="s">
+      <c r="J755" s="38" t="s">
         <v>1433</v>
       </c>
       <c r="K755" s="8" t="s">
@@ -32822,7 +32821,7 @@
       <c r="G756" s="9"/>
       <c r="H756" s="9"/>
       <c r="I756" s="9"/>
-      <c r="J756" s="39" t="s">
+      <c r="J756" s="38" t="s">
         <v>1435</v>
       </c>
       <c r="K756" s="8" t="s">
@@ -32857,7 +32856,7 @@
       <c r="G757" s="9"/>
       <c r="H757" s="9"/>
       <c r="I757" s="9"/>
-      <c r="J757" s="39" t="s">
+      <c r="J757" s="38" t="s">
         <v>1437</v>
       </c>
       <c r="K757" s="8" t="s">
@@ -32892,7 +32891,7 @@
       <c r="G758" s="9"/>
       <c r="H758" s="9"/>
       <c r="I758" s="9"/>
-      <c r="J758" s="39" t="s">
+      <c r="J758" s="38" t="s">
         <v>1439</v>
       </c>
       <c r="K758" s="8" t="s">
@@ -32927,7 +32926,7 @@
       <c r="G759" s="9"/>
       <c r="H759" s="9"/>
       <c r="I759" s="9"/>
-      <c r="J759" s="39" t="s">
+      <c r="J759" s="38" t="s">
         <v>1441</v>
       </c>
       <c r="K759" s="8" t="s">
@@ -32962,7 +32961,7 @@
       <c r="G760" s="9"/>
       <c r="H760" s="9"/>
       <c r="I760" s="9"/>
-      <c r="J760" s="39" t="s">
+      <c r="J760" s="38" t="s">
         <v>1443</v>
       </c>
       <c r="K760" s="8" t="s">
@@ -32997,7 +32996,7 @@
       <c r="G761" s="9"/>
       <c r="H761" s="9"/>
       <c r="I761" s="9"/>
-      <c r="J761" s="39" t="s">
+      <c r="J761" s="38" t="s">
         <v>1445</v>
       </c>
       <c r="K761" s="8" t="s">
@@ -33032,7 +33031,7 @@
       <c r="G762" s="9"/>
       <c r="H762" s="9"/>
       <c r="I762" s="9"/>
-      <c r="J762" s="39" t="s">
+      <c r="J762" s="38" t="s">
         <v>1447</v>
       </c>
       <c r="K762" s="8" t="s">
@@ -33067,7 +33066,7 @@
       <c r="G763" s="9"/>
       <c r="H763" s="9"/>
       <c r="I763" s="9"/>
-      <c r="J763" s="39" t="s">
+      <c r="J763" s="38" t="s">
         <v>1449</v>
       </c>
       <c r="K763" s="8" t="s">
@@ -33102,7 +33101,7 @@
       <c r="G764" s="9"/>
       <c r="H764" s="9"/>
       <c r="I764" s="9"/>
-      <c r="J764" s="39" t="s">
+      <c r="J764" s="38" t="s">
         <v>1451</v>
       </c>
       <c r="K764" s="8" t="s">
@@ -33137,7 +33136,7 @@
       <c r="G765" s="9"/>
       <c r="H765" s="9"/>
       <c r="I765" s="9"/>
-      <c r="J765" s="39" t="s">
+      <c r="J765" s="38" t="s">
         <v>1453</v>
       </c>
       <c r="K765" s="8" t="s">
@@ -33172,7 +33171,7 @@
       <c r="G766" s="9"/>
       <c r="H766" s="9"/>
       <c r="I766" s="9"/>
-      <c r="J766" s="39" t="s">
+      <c r="J766" s="38" t="s">
         <v>1455</v>
       </c>
       <c r="K766" s="8" t="s">
@@ -33207,7 +33206,7 @@
       <c r="G767" s="9"/>
       <c r="H767" s="9"/>
       <c r="I767" s="9"/>
-      <c r="J767" s="39" t="s">
+      <c r="J767" s="38" t="s">
         <v>1457</v>
       </c>
       <c r="K767" s="8" t="s">
@@ -33382,7 +33381,7 @@
       <c r="G772" s="9"/>
       <c r="H772" s="9"/>
       <c r="I772" s="9"/>
-      <c r="J772" s="39" t="s">
+      <c r="J772" s="38" t="s">
         <v>1467</v>
       </c>
       <c r="K772" s="8" t="s">
@@ -36322,7 +36321,7 @@
       <c r="G856" s="9"/>
       <c r="H856" s="9"/>
       <c r="I856" s="9"/>
-      <c r="J856" s="42" t="s">
+      <c r="J856" s="41" t="s">
         <v>1636</v>
       </c>
       <c r="K856" s="8" t="s">
@@ -36331,10 +36330,10 @@
       <c r="L856" s="8">
         <v>214000</v>
       </c>
-      <c r="M856" s="43">
+      <c r="M856" s="42">
         <v>44902</v>
       </c>
-      <c r="N856" s="43">
+      <c r="N856" s="42">
         <v>44824</v>
       </c>
     </row>
@@ -36357,7 +36356,7 @@
       <c r="G857" s="9"/>
       <c r="H857" s="9"/>
       <c r="I857" s="9"/>
-      <c r="J857" s="42" t="s">
+      <c r="J857" s="41" t="s">
         <v>1638</v>
       </c>
       <c r="K857" s="8" t="s">
@@ -36366,10 +36365,10 @@
       <c r="L857" s="8">
         <v>214000</v>
       </c>
-      <c r="M857" s="43">
+      <c r="M857" s="42">
         <v>44902</v>
       </c>
-      <c r="N857" s="43">
+      <c r="N857" s="42">
         <v>44824</v>
       </c>
     </row>
@@ -36392,7 +36391,7 @@
       <c r="G858" s="9"/>
       <c r="H858" s="9"/>
       <c r="I858" s="9"/>
-      <c r="J858" s="42" t="s">
+      <c r="J858" s="41" t="s">
         <v>1640</v>
       </c>
       <c r="K858" s="8" t="s">
@@ -36401,10 +36400,10 @@
       <c r="L858" s="8">
         <v>214000</v>
       </c>
-      <c r="M858" s="43">
+      <c r="M858" s="42">
         <v>44902</v>
       </c>
-      <c r="N858" s="43">
+      <c r="N858" s="42">
         <v>44848</v>
       </c>
     </row>
@@ -36427,7 +36426,7 @@
       <c r="G859" s="9"/>
       <c r="H859" s="9"/>
       <c r="I859" s="9"/>
-      <c r="J859" s="42" t="s">
+      <c r="J859" s="41" t="s">
         <v>1642</v>
       </c>
       <c r="K859" s="8" t="s">
@@ -36462,7 +36461,7 @@
       <c r="G860" s="9"/>
       <c r="H860" s="9"/>
       <c r="I860" s="9"/>
-      <c r="J860" s="39" t="s">
+      <c r="J860" s="38" t="s">
         <v>1644</v>
       </c>
       <c r="K860" s="8" t="s">
@@ -36497,7 +36496,7 @@
       <c r="G861" s="9"/>
       <c r="H861" s="9"/>
       <c r="I861" s="9"/>
-      <c r="J861" s="39" t="s">
+      <c r="J861" s="38" t="s">
         <v>1646</v>
       </c>
       <c r="K861" s="8" t="s">
@@ -36532,7 +36531,7 @@
       <c r="G862" s="9"/>
       <c r="H862" s="9"/>
       <c r="I862" s="9"/>
-      <c r="J862" s="39" t="s">
+      <c r="J862" s="38" t="s">
         <v>1648</v>
       </c>
       <c r="K862" s="8" t="s">
@@ -36567,7 +36566,7 @@
       <c r="G863" s="9"/>
       <c r="H863" s="9"/>
       <c r="I863" s="9"/>
-      <c r="J863" s="39" t="s">
+      <c r="J863" s="38" t="s">
         <v>1650</v>
       </c>
       <c r="K863" s="8" t="s">
@@ -36602,7 +36601,7 @@
       <c r="G864" s="9"/>
       <c r="H864" s="9"/>
       <c r="I864" s="9"/>
-      <c r="J864" s="39" t="s">
+      <c r="J864" s="38" t="s">
         <v>1652</v>
       </c>
       <c r="K864" s="8" t="s">
@@ -36637,7 +36636,7 @@
       <c r="G865" s="9"/>
       <c r="H865" s="9"/>
       <c r="I865" s="9"/>
-      <c r="J865" s="44" t="s">
+      <c r="J865" s="43" t="s">
         <v>1654</v>
       </c>
       <c r="K865" s="8" t="s">
@@ -36672,7 +36671,7 @@
       <c r="G866" s="9"/>
       <c r="H866" s="9"/>
       <c r="I866" s="9"/>
-      <c r="J866" s="44" t="s">
+      <c r="J866" s="43" t="s">
         <v>1656</v>
       </c>
       <c r="K866" s="8" t="s">
@@ -36707,7 +36706,7 @@
       <c r="G867" s="9"/>
       <c r="H867" s="9"/>
       <c r="I867" s="9"/>
-      <c r="J867" s="44" t="s">
+      <c r="J867" s="43" t="s">
         <v>1658</v>
       </c>
       <c r="K867" s="8" t="s">
@@ -36742,7 +36741,7 @@
       <c r="G868" s="9"/>
       <c r="H868" s="9"/>
       <c r="I868" s="9"/>
-      <c r="J868" s="44" t="s">
+      <c r="J868" s="43" t="s">
         <v>1660</v>
       </c>
       <c r="K868" s="8" t="s">
@@ -36777,7 +36776,7 @@
       <c r="G869" s="9"/>
       <c r="H869" s="9"/>
       <c r="I869" s="9"/>
-      <c r="J869" s="42" t="s">
+      <c r="J869" s="41" t="s">
         <v>1663</v>
       </c>
       <c r="K869" s="8" t="s">
@@ -36786,10 +36785,10 @@
       <c r="L869" s="8">
         <v>308754</v>
       </c>
-      <c r="M869" s="43">
+      <c r="M869" s="42">
         <v>45828</v>
       </c>
-      <c r="N869" s="43">
+      <c r="N869" s="42">
         <v>45790</v>
       </c>
     </row>
@@ -36812,7 +36811,7 @@
       <c r="G870" s="9"/>
       <c r="H870" s="9"/>
       <c r="I870" s="9"/>
-      <c r="J870" s="42" t="s">
+      <c r="J870" s="41" t="s">
         <v>1665</v>
       </c>
       <c r="K870" s="8" t="s">
@@ -36821,10 +36820,10 @@
       <c r="L870" s="8">
         <v>308754</v>
       </c>
-      <c r="M870" s="43">
+      <c r="M870" s="42">
         <v>45828</v>
       </c>
-      <c r="N870" s="43">
+      <c r="N870" s="42">
         <v>45803</v>
       </c>
     </row>
@@ -36847,7 +36846,7 @@
       <c r="G871" s="9"/>
       <c r="H871" s="9"/>
       <c r="I871" s="9"/>
-      <c r="J871" s="39" t="s">
+      <c r="J871" s="38" t="s">
         <v>1667</v>
       </c>
       <c r="K871" s="8" t="s">
@@ -36856,7 +36855,7 @@
       <c r="L871" s="8">
         <v>542809</v>
       </c>
-      <c r="M871" s="43">
+      <c r="M871" s="42">
         <v>45919</v>
       </c>
       <c r="N871" s="24">
@@ -36882,19 +36881,19 @@
       <c r="G872" s="9"/>
       <c r="H872" s="9"/>
       <c r="I872" s="9"/>
-      <c r="J872" s="45" t="s">
+      <c r="J872" s="44" t="s">
         <v>1670</v>
       </c>
       <c r="K872" s="8" t="s">
         <v>1671</v>
       </c>
-      <c r="L872" s="46">
+      <c r="L872" s="45">
         <v>214000</v>
       </c>
-      <c r="M872" s="47">
+      <c r="M872" s="46">
         <v>45037</v>
       </c>
-      <c r="N872" s="47">
+      <c r="N872" s="46">
         <v>44943</v>
       </c>
     </row>
@@ -36917,7 +36916,7 @@
       <c r="G873" s="9"/>
       <c r="H873" s="9"/>
       <c r="I873" s="9"/>
-      <c r="J873" s="48" t="s">
+      <c r="J873" s="47" t="s">
         <v>1673</v>
       </c>
       <c r="K873" s="8" t="s">
@@ -36934,7 +36933,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M873" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="J1:N873" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
